--- a/data/trans_dic/P1803_2016_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1803_2016_2023-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 10,33</t>
+          <t>4,93; 10,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,77; 17,51</t>
+          <t>9,7; 15,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 10,94</t>
+          <t>5,02; 10,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 20,07</t>
+          <t>13,6; 19,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,6</t>
+          <t>5,64; 9,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,11; 17,69</t>
+          <t>12,32; 16,5</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,32</t>
+          <t>2,03; 6,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 11,12</t>
+          <t>5,55; 10,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 11,94</t>
+          <t>6,06; 12,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 18,79</t>
+          <t>12,49; 18,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,17</t>
+          <t>4,68; 8,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 13,62</t>
+          <t>9,19; 13,26</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,83</t>
+          <t>3,05; 6,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 77,27</t>
+          <t>7,59; 13,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 12,14</t>
+          <t>3,69; 11,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 12,98</t>
+          <t>6,25; 13,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,1</t>
+          <t>3,74; 7,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,18; 70,03</t>
+          <t>7,79; 12,49</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,82</t>
+          <t>3,4; 6,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,6</t>
+          <t>5,3; 8,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 8,2</t>
+          <t>4,76; 8,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 11,51</t>
+          <t>8,41; 11,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,42</t>
+          <t>4,24; 6,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,23</t>
+          <t>7,07; 9,46</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,33</t>
+          <t>2,25; 5,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 9,24</t>
+          <t>4,03; 8,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,9</t>
+          <t>2,95; 6,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 9,39</t>
+          <t>6,97; 10,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,03</t>
+          <t>3,02; 5,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 8,69</t>
+          <t>6,12; 8,78</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,63</t>
+          <t>1,63; 6,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 13,49</t>
+          <t>1,84; 12,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,26</t>
+          <t>2,85; 5,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,16; 7,46</t>
+          <t>4,28; 7,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,19</t>
+          <t>2,88; 5,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,94</t>
+          <t>4,2; 7,41</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,36</t>
+          <t>3,86; 5,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 30,5</t>
+          <t>7,13; 9,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 6,42</t>
+          <t>4,78; 6,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,01; 10,7</t>
+          <t>9,25; 10,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 5,65</t>
+          <t>4,52; 5,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,79; 23,74</t>
+          <t>8,43; 9,79</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69295</t>
+          <t>69563</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76502</t>
+          <t>80368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>145797</t>
+          <t>149931</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22067; 44305</t>
+          <t>21164; 44564</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54405; 88440</t>
+          <t>53401; 87048</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17307; 37960</t>
+          <t>17436; 37239</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61773; 89813</t>
+          <t>66433; 94736</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45088; 74542</t>
+          <t>43804; 73967</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>124944; 168542</t>
+          <t>127998; 171454</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>37306</t>
+          <t>37572</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59035</t>
+          <t>63873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96341</t>
+          <t>101445</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8239; 23830</t>
+          <t>7645; 23505</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27499; 50297</t>
+          <t>26830; 50958</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22186; 44448</t>
+          <t>22543; 45869</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48446; 71892</t>
+          <t>52836; 77798</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33367; 61217</t>
+          <t>35070; 62754</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80983; 113734</t>
+          <t>83327; 120206</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>286992</t>
+          <t>47990</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15401</t>
+          <t>16995</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>302393</t>
+          <t>64984</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16060; 35653</t>
+          <t>15898; 36330</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58595; 516397</t>
+          <t>35815; 64725</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6083; 20160</t>
+          <t>6123; 19849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10366; 21668</t>
+          <t>11727; 24425</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25300; 48883</t>
+          <t>25726; 49174</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76698; 584901</t>
+          <t>51372; 82334</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>70644</t>
+          <t>76240</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84094</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>154738</t>
+          <t>163135</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38113; 66957</t>
+          <t>39063; 69405</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56056; 89029</t>
+          <t>60042; 96934</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39026; 67733</t>
+          <t>39300; 68638</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41485; 112496</t>
+          <t>72379; 102744</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84495; 126819</t>
+          <t>83791; 125069</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>105103; 185839</t>
+          <t>140858; 188419</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30971</t>
+          <t>33220</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63927</t>
+          <t>69702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94899</t>
+          <t>102921</t>
         </is>
       </c>
     </row>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14446; 33112</t>
+          <t>13943; 31157</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20597; 43912</t>
+          <t>22889; 48632</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20766; 43523</t>
+          <t>21807; 45028</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47677; 79000</t>
+          <t>57915; 83908</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40408; 68414</t>
+          <t>41077; 71074</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73971; 114443</t>
+          <t>85592; 122883</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14385</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42203</t>
+          <t>47351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56588</t>
+          <t>59768</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5110; 19036</t>
+          <t>4691; 18172</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4186; 32446</t>
+          <t>4357; 29184</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30365; 56880</t>
+          <t>30879; 60561</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31663; 56753</t>
+          <t>36131; 64003</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>39985; 71096</t>
+          <t>39430; 72641</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42718; 79465</t>
+          <t>45391; 80075</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>509593</t>
+          <t>277002</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>341163</t>
+          <t>365182</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>850756</t>
+          <t>642184</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>130317; 181371</t>
+          <t>130802; 180451</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>275062; 1029749</t>
+          <t>245388; 315149</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>167980; 226806</t>
+          <t>168837; 223084</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>286374; 382581</t>
+          <t>336110; 395059</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>314070; 390752</t>
+          <t>312544; 389216</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>611096; 1650639</t>
+          <t>596520; 693071</t>
         </is>
       </c>
     </row>
